--- a/ImpactNode/OutputJob/BOM/Bill of Materials-ImpactNode.xlsx
+++ b/ImpactNode/OutputJob/BOM/Bill of Materials-ImpactNode.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\safan\OneDrive\Desktop\embedded-works\ImpactNode\OutputJob\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3BF98226-6827-4526-98FE-0D37A6D351B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2ADB613E-73CD-4BE0-8C08-6FCDEA03BB22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1530" yWindow="1270" windowWidth="14380" windowHeight="7270" xr2:uid="{769C97D9-8888-44F6-A06A-24CE9969C446}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{769C97D9-8888-44F6-A06A-24CE9969C446}"/>
   </bookViews>
   <sheets>
     <sheet name="Bill of Materials-ImpactNode" sheetId="1" r:id="rId1"/>
